--- a/safety_data.xlsx
+++ b/safety_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\Streamlit_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591ADF65-78DD-4CAD-9079-A1C71E658912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80106DC1-AC61-4E4A-9492-44AC51E86215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{97F4F0D8-AB31-4CDF-B634-2F369659B5B3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
   <si>
     <t>가설공사</t>
   </si>
@@ -44,38 +44,179 @@
     <t>시스템 비계 수직재 간격 기준은?</t>
   </si>
   <si>
-    <t>[KOSHA GUIDE C-49-2015]에 따르면... (긴 내용)</t>
-  </si>
-  <si>
-    <t>KOSHA GUIDE</t>
-  </si>
-  <si>
     <t>안전교육</t>
   </si>
   <si>
-    <t>신규 채용자 교육 시간은?</t>
-  </si>
-  <si>
-    <t>산업안전보건법 시행규칙에 따라... (긴 내용)</t>
-  </si>
-  <si>
-    <t>산안법 시행규칙</t>
-  </si>
-  <si>
     <t>category</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>question</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>context</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>source</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOSHA GUIDE C-49-2015</t>
+  </si>
+  <si>
+    <t>이동식 비계 사용할 때 안전수칙 알려줘</t>
+  </si>
+  <si>
+    <t>산안법 규칙 제68조</t>
+  </si>
+  <si>
+    <t>사다리 위에서 작업해도 됨? 사다리 작업 기준</t>
+  </si>
+  <si>
+    <t>K-사다리 안전지침</t>
+  </si>
+  <si>
+    <t>신규 채용자 교육 시간은 몇 시간이야?</t>
+  </si>
+  <si>
+    <t>산안법 시행규칙 별표4</t>
+  </si>
+  <si>
+    <t>TBM이 뭐야? 언제 해야 돼?</t>
+  </si>
+  <si>
+    <t>KOSHA 안전보건매뉴얼</t>
+  </si>
+  <si>
+    <t>콘크리트</t>
+  </si>
+  <si>
+    <t>비 오는 날 콘크리트 타설 해도 되나요? (우천 타설)</t>
+  </si>
+  <si>
+    <t>KCS 14 20 10</t>
+  </si>
+  <si>
+    <t>겨울철 콘크리트 보양 주의사항 (갈탄 사용)</t>
+  </si>
+  <si>
+    <t>한중 콘크리트 가이드</t>
+  </si>
+  <si>
+    <t>중장비</t>
+  </si>
+  <si>
+    <t>굴착기 퀵커플러 안전 조치 (바가지 떨어짐 방지)</t>
+  </si>
+  <si>
+    <t>건설기계 안전기준</t>
+  </si>
+  <si>
+    <t>크레인 작업 중단 바람 세기 기준 (풍속)</t>
+  </si>
+  <si>
+    <t>산안법 규칙 제37조</t>
+  </si>
+  <si>
+    <t>안전관리비</t>
+  </si>
+  <si>
+    <t>안전관리비로 신호수 인건비 줄 수 있어?</t>
+  </si>
+  <si>
+    <t>고용노동부 고시</t>
+  </si>
+  <si>
+    <t>보호구</t>
+  </si>
+  <si>
+    <t>안전모 종류랑 교체 주기 알려줘</t>
+  </si>
+  <si>
+    <t>보호구 안전인증 고시</t>
+  </si>
+  <si>
+    <t>밀폐공간</t>
+  </si>
+  <si>
+    <t>밀폐공간 작업 시 필수 장비랑 절차</t>
+  </si>
+  <si>
+    <t>KOSHA 매뉴얼</t>
+  </si>
+  <si>
+    <t>철골공사</t>
+  </si>
+  <si>
+    <t>철골 작업 중지 기준 (날씨)</t>
+  </si>
+  <si>
+    <t>산안법 규칙 제383조</t>
+  </si>
+  <si>
+    <t>화재예방</t>
+  </si>
+  <si>
+    <t>용접 작업 할 때 화재감시자 배치해야 돼?</t>
+  </si>
+  <si>
+    <t>산안법 규칙 제241조의2</t>
+  </si>
+  <si>
+    <t>휴식</t>
+  </si>
+  <si>
+    <t>폭염 주의보 발령 시 근로자 휴식 기준</t>
+  </si>
+  <si>
+    <t>고용노동부 가이드라인</t>
+  </si>
+  <si>
+    <t>[KOSHA GUIDE C-49-2015] 시스템 비계 안전작업 지침에 따르면:1. 수직재의 간격은 구조검토 결과에 따라야 하나, 일반적으로 띠장 방향 1.8m 이하, 장선 방향 1.5m 이하로 설치한다.2. 수직재 연결부는 전용 철물을 사용하고, 이음 위치가 한 곳에 집중되지 않도록 엇갈리게 배치한다.</t>
+  </si>
+  <si>
+    <t>[산업안전보건기준에 관한 규칙 제68조]1. 바퀴에는 불시 이동을 막기 위한 브레이크(Stopper)를 반드시 체결한다.2. 비계의 최대 높이는 밑변 최소폭의 4배 이하로 한다. (전도 방지)3. 작업 발판 주변에는 안전난간을 설치하고, 승강용 사다리를 부착해야 한다.4. 작업자가 탑승한 상태에서 비계를 이동시키는 것은 절대 금지한다.</t>
+  </si>
+  <si>
+    <t>[이동식 사다리 안전작업 지침]1. 원칙: 사다리는 이동 통로로만 사용하는 것이 원칙이다.2. 예외: 좁은 장소 등 비계 설치가 곤란한 경우에 한해, 2인 1조(1인은 지지)로 평탄한 곳에서만 제한적으로 작업 가능.3. 높이 3.5m 초과 시에는 사다리 작업 금지.4. 최상부 발판에서는 작업 금지. 반드시 안전모 착용.</t>
+  </si>
+  <si>
+    <t>[산업안전보건법 시행규칙 별표 4]1. 일용근로자: 1시간 이상 (단, 건설업 기초안전보건교육 이수증 소지 시 면제 가능)2. 상용근로자(일용직 제외): 8시간 이상3. 교육내용: 산업안전 및 사고 예방, 보호구 착용 및 관리, 물질안전보건자료(MSDS) 등.</t>
+  </si>
+  <si>
+    <t>[TBM (Tool Box Meeting) 가이드]1. 정의: 작업 개시 전, 작업 현장 근처에서 관리감독자와 작업자들이 모여 작업 내용과 위험 요인을 공유하는 활동.2. 시간: 보통 작업 시작 전 10분 내외로 진행.3. 내용: 당일 작업 절차, 위험 포인트, 개인 보호구 착용 상태 확인, 건강 상태 확인(음주 여부 등).</t>
+  </si>
+  <si>
+    <t>[콘크리트 표준시방서 KCS 14 20 10]1. 원칙: 강우 시 타설은 품질 저하(강도 부족) 우려로 금지한다.2. 예외: 부득이한 경우 책임감리원의 승인을 받아야 하며, 물-시멘트비 조정 및 천막 보양(빗물 유입 차단) 조치를 완벽히 해야 한다.3. 빗물이 콘크리트에 섞이면 강도가 급격히 떨어지므로 즉시 작업을 중단하는 것이 권장된다.</t>
+  </si>
+  <si>
+    <t>[한중 콘크리트 시공 가이드]1. 초기 동해 방지를 위해 압축강도가 5MPa 나올 때까지 0℃ 이상 유지 필요.2. 갈탄 사용 시 일산화탄소 중독 사고 위험이 매우 높음.3. 필수 조치: 작업자 출입 전 반드시 산소 및 유해가스 농도 측정, 환기 설비 가동, 질식 재해 예방 교육 실시. 전열기구 사용 권장.</t>
+  </si>
+  <si>
+    <t>[건설기계 안전기준]1. 퀵커플러(버킷 연결 장치) 사용 시, 운전석에서 잠금 스위치를 조작한 후 반드시 '안전핀(Safety Pin)'을 체결해야 한다.2. 최근 자동 안전장치가 있더라도, 육안으로 체결 상태를 확인 후 작업해야 한다.3. 인양 작업용으로 사용하는 것은 원칙적으로 금지된다.</t>
+  </si>
+  <si>
+    <t>[산업안전보건기준에 관한 규칙 제37조]1. 순간풍속 10m/s 초과: 타워크레인 설치, 해체, 수리, 점검 작업 중지.2. 순간풍속 15m/s 초과: 타워크레인 운전 작업 중지 (크레인이 넘어갈 위험).3. 강풍 예보 시 지브(Jib)가 바람 부는 방향으로 자연스럽게 회전하도록 브레이크를 풀어두어야 한다(Weathervaning).</t>
+  </si>
+  <si>
+    <t>[건설업 산업안전보건관리비 계상 및 사용기준]1. 원칙: 신호수 인건비는 공사비(직접노무비)에 포함되므로 안전관리비 사용 불가.2. 예외: '유도자'의 경우 사용 가능했으나 규정이 까다로움. 3. 최신 변경: 중장비 등 차량계 건설기계의 유도 업무를 전담하는 사람의 인건비는 제한적으로 사용 가능할 수 있으니 발주처와 사전 협의 필요. (기본적으로는 불가하다고 보는 것이 보수적임)</t>
+  </si>
+  <si>
+    <t>[보호구 안전인증 고시]1. 종류: AB형(낙하/추락 방지), AE형(낙하/감전 방지), ABE형(낙하/추락/감전 모두 방지 - 건설현장용).2. 교체 주기: 플라스틱 제품은 자외선 등에 의해 노화되므로 통상 1년~2년 사용 후 교체 권장. 충격을 한 번이라도 받은 헬멧은 겉보기에 멀쩡해도 즉시 폐기해야 한다.</t>
+  </si>
+  <si>
+    <t>[밀폐공간 질식재해 예방 매뉴얼]1. 절차: 허가서 발급 → 산소 농도 측정(작업 전/중) → 환기 실시 → 보호구 착용 후 작업.2. 기준: 산소 농도 18% 미만은 산소 결핍.3. 필수 장비: 복합가스 측정기, 환기팬(송풍기/배풍기), 송기 마스크(공기호흡기), 무전기, 삼각대(구조용).</t>
+  </si>
+  <si>
+    <t>[산업안전보건기준에 관한 규칙 제383조]다음의 기상 상태에서는 철골 조립 작업을 중지해야 한다.1. 풍속: 초당 10미터 이상2. 강우량: 시간당 1밀리미터 이상3. 강설량: 시간당 1센티미터 이상단, 위험을 방지하기 위한 조치가 된 경우 감리원의 승인 하에 가능.</t>
+  </si>
+  <si>
+    <t>[산업안전보건기준에 관한 규칙 제241조의2]1. 배치 기준: 불꽃이 튀는 용접/용단 작업 시 반경 11m 이내에 가연성 물질이 있거나 화재 위험이 있는 경우 반드시 화재감시자를 배치해야 한다.2. 화재감시자의 임무: 화재 감시, 소화기 비치(휴대용 조명 포함), 비상시 근로자 대피 유도.3. 화재감시자는 다른 업무(자재 정리 등)를 겸임할 수 없다.</t>
+  </si>
+  <si>
+    <t>[온열질환 예방 가이드]1. 폭염주의보(체감 33℃): 매 시간 10분 휴식 권장, 14:00~17:00 옥외 작업 단축.2. 폭염경보(체감 35℃): 매 시간 15분 휴식 권장, 14:00~17:00 옥외 작업 중지 강력 권고.3. 3대 수칙: 물(시원한 물), 그늘(휴게소), 휴식(규칙적으로).</t>
   </si>
 </sst>
 </file>
@@ -92,12 +233,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
@@ -111,6 +246,12 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -120,7 +261,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -143,21 +284,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -493,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AB65259-10B2-4A2F-B540-0680E3F566A8}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.625" customWidth="1"/>
@@ -504,19 +663,19 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -524,28 +683,210 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="90" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>